--- a/TEDI_Ham_chui_model/TEDI_Ham_chui_model/New Microsoft Excel Worksheet (3).xlsx
+++ b/TEDI_Ham_chui_model/TEDI_Ham_chui_model/New Microsoft Excel Worksheet (3).xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\TEDI-Ham_chui\TEDI_Ham_chui_model\TEDI_Ham_chui_model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F75556D-FD9E-4F99-9CF1-5B9E68C676B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF1BFF2-9930-4E60-8EF2-9EBD8BC4AEBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="28">
-  <si>
-    <t>Type Name</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="28">
   <si>
     <t>BanQuaDoPhai 1</t>
   </si>
@@ -45,9 +42,6 @@
     <t>FamilyCongHamChui-HT</t>
   </si>
   <si>
-    <t>TuongCanhPhai 2</t>
-  </si>
-  <si>
     <t>TuongCanhPhai 1</t>
   </si>
   <si>
@@ -57,9 +51,6 @@
     <t>TuongCanhTrai 1</t>
   </si>
   <si>
-    <t>Parameter</t>
-  </si>
-  <si>
     <t>Chamfer</t>
   </si>
   <si>
@@ -96,9 +87,6 @@
     <t>H3</t>
   </si>
   <si>
-    <t>Giá trị</t>
-  </si>
-  <si>
     <t>Hw2</t>
   </si>
   <si>
@@ -109,19 +97,60 @@
   </si>
   <si>
     <t>Lw</t>
+  </si>
+  <si>
+    <t>l_tai</t>
+  </si>
+  <si>
+    <t>độ</t>
+  </si>
+  <si>
+    <t>mm</t>
+  </si>
+  <si>
+    <t>%</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="3" tint="0.39997558519241921"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -159,15 +188,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -449,326 +490,349 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6CCFDC2-B183-406D-BD8F-F59AB7FCD01D}">
+  <dimension ref="A1:AQ3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.21875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="8.88671875" style="1"/>
-    <col min="9" max="9" width="57.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="14" width="8.88671875" style="1"/>
-    <col min="15" max="15" width="20.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="7"/>
+      <c r="S1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="T1" s="7"/>
+      <c r="U1" s="7"/>
+      <c r="V1" s="7"/>
+      <c r="W1" s="7"/>
+      <c r="X1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y1" s="7"/>
+      <c r="Z1" s="7"/>
+      <c r="AA1" s="7"/>
+      <c r="AB1" s="7"/>
+      <c r="AC1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD1" s="7"/>
+      <c r="AE1" s="7"/>
+      <c r="AF1" s="7"/>
+      <c r="AG1" s="7"/>
+      <c r="AH1" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI1" s="7"/>
+      <c r="AJ1" s="7"/>
+      <c r="AK1" s="7"/>
+      <c r="AL1" s="7"/>
+      <c r="AM1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="AN1" s="7"/>
+      <c r="AO1" s="7"/>
+      <c r="AP1" s="7"/>
+      <c r="AQ1" s="7"/>
+    </row>
+    <row r="2" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="D2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="W2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="X2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="AH2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI2" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="AJ2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK2" s="6" t="s">
         <v>23</v>
       </c>
+      <c r="AL2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="AN2" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="AO2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="AP2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AQ2" s="6" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="2"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="2"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="2"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="2"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="2"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="2"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="2"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="2"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="2"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="2"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C14" s="2"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="2"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="2"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="2"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C18" s="2"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="2"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C22" s="2"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="2"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="2"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="2"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C26" s="2"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="2"/>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="2"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="2"/>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C30" s="2"/>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="2"/>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="2"/>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
+      <c r="K3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="2"/>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="2"/>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
+      <c r="S3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AK3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C35" s="2"/>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="2"/>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B37" s="3"/>
-      <c r="C37" s="2"/>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B38" s="3"/>
-      <c r="C38" s="2"/>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B39" s="3"/>
-      <c r="C39" s="2"/>
+      <c r="AM3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AP3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AQ3" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="B35:B39"/>
-    <mergeCell ref="B2:B7"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="B18:B21"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="B30:B34"/>
+    <mergeCell ref="X1:AB1"/>
+    <mergeCell ref="AC1:AG1"/>
+    <mergeCell ref="AH1:AL1"/>
+    <mergeCell ref="AM1:AQ1"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="N1:R1"/>
+    <mergeCell ref="S1:W1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
